--- a/output/roomself_excel/12239.xlsx
+++ b/output/roomself_excel/12239.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>522404</v>
+        <v>210060</v>
       </c>
       <c r="D2" t="n">
-        <v>8684</v>
+        <v>4032</v>
       </c>
       <c r="E2" t="n">
-        <v>1343</v>
+        <v>552</v>
       </c>
       <c r="F2" t="n">
-        <v>889</v>
+        <v>450</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>133320</v>
+        <v>215530</v>
       </c>
       <c r="D3" t="n">
-        <v>2972</v>
+        <v>3808</v>
       </c>
       <c r="E3" t="n">
-        <v>472</v>
+        <v>632</v>
       </c>
       <c r="F3" t="n">
-        <v>335</v>
+        <v>405</v>
       </c>
     </row>
     <row r="4">
@@ -514,16 +514,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>119113</v>
+        <v>133320</v>
       </c>
       <c r="D4" t="n">
-        <v>2776</v>
+        <v>2972</v>
       </c>
       <c r="E4" t="n">
-        <v>632</v>
+        <v>472</v>
       </c>
       <c r="F4" t="n">
-        <v>343</v>
+        <v>335</v>
       </c>
     </row>
     <row r="5">
@@ -536,16 +536,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>97006</v>
+        <v>119113</v>
       </c>
       <c r="D5" t="n">
-        <v>2500</v>
+        <v>2776</v>
       </c>
       <c r="E5" t="n">
-        <v>338</v>
+        <v>438</v>
       </c>
       <c r="F5" t="n">
-        <v>32</v>
+        <v>343</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>76068</v>
+        <v>97006</v>
       </c>
       <c r="D6" t="n">
-        <v>2688</v>
+        <v>2500</v>
       </c>
       <c r="E6" t="n">
-        <v>552</v>
+        <v>338</v>
       </c>
       <c r="F6" t="n">
-        <v>385</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7">
@@ -576,19 +576,63 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>Bath</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>76068</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2688</v>
+      </c>
+      <c r="E7" t="n">
+        <v>385</v>
+      </c>
+      <c r="F7" t="n">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Hallway</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>96814</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2876</v>
+      </c>
+      <c r="E8" t="n">
+        <v>546</v>
+      </c>
+      <c r="F8" t="n">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="C9" t="n">
         <v>30107</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D9" t="n">
         <v>1392</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E9" t="n">
         <v>187</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F9" t="n">
         <v>32</v>
       </c>
     </row>

--- a/output/roomself_excel/12239.xlsx
+++ b/output/roomself_excel/12239.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,47 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
         </is>
       </c>
     </row>
@@ -475,12 +510,31 @@
       <c r="D2" t="n">
         <v>4032</v>
       </c>
-      <c r="E2" t="n">
-        <v>552</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>450</v>
-      </c>
+        <v>419</v>
+      </c>
+      <c r="G2" t="n">
+        <v>32</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>165</v>
+      </c>
+      <c r="J2" t="n">
+        <v>22</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,11 +551,38 @@
       <c r="D3" t="n">
         <v>3808</v>
       </c>
-      <c r="E3" t="n">
-        <v>632</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>405</v>
+        <v>373</v>
+      </c>
+      <c r="G3" t="n">
+        <v>32</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>162</v>
+      </c>
+      <c r="J3" t="n">
+        <v>32</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>305</v>
+      </c>
+      <c r="M3" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="4">
@@ -519,12 +600,31 @@
       <c r="D4" t="n">
         <v>2972</v>
       </c>
-      <c r="E4" t="n">
-        <v>472</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>335</v>
-      </c>
+        <v>440</v>
+      </c>
+      <c r="G4" t="n">
+        <v>32</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>303</v>
+      </c>
+      <c r="J4" t="n">
+        <v>32</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,11 +641,38 @@
       <c r="D5" t="n">
         <v>2776</v>
       </c>
-      <c r="E5" t="n">
-        <v>438</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>343</v>
+        <v>291</v>
+      </c>
+      <c r="G5" t="n">
+        <v>32</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>383</v>
+      </c>
+      <c r="J5" t="n">
+        <v>32</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>311</v>
+      </c>
+      <c r="M5" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="6">
@@ -563,12 +690,23 @@
       <c r="D6" t="n">
         <v>2500</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
         <v>338</v>
       </c>
-      <c r="F6" t="n">
-        <v>32</v>
-      </c>
+      <c r="G6" t="n">
+        <v>32</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,11 +723,38 @@
       <c r="D7" t="n">
         <v>2688</v>
       </c>
-      <c r="E7" t="n">
-        <v>385</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F7" t="n">
-        <v>344</v>
+        <v>186</v>
+      </c>
+      <c r="G7" t="n">
+        <v>32</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>201</v>
+      </c>
+      <c r="J7" t="n">
+        <v>25</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>114</v>
+      </c>
+      <c r="M7" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="8">
@@ -607,11 +772,38 @@
       <c r="D8" t="n">
         <v>2876</v>
       </c>
-      <c r="E8" t="n">
-        <v>546</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F8" t="n">
-        <v>208</v>
+        <v>417</v>
+      </c>
+      <c r="G8" t="n">
+        <v>22</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>104</v>
+      </c>
+      <c r="J8" t="n">
+        <v>83</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>125</v>
+      </c>
+      <c r="M8" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="9">
@@ -629,12 +821,31 @@
       <c r="D9" t="n">
         <v>1392</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
         <v>187</v>
       </c>
-      <c r="F9" t="n">
-        <v>32</v>
-      </c>
+      <c r="G9" t="n">
+        <v>32</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>161</v>
+      </c>
+      <c r="J9" t="n">
+        <v>23</v>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
